--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="607">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251017120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-17T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -138,7 +138,7 @@
     <t>07</t>
   </si>
   <si>
-    <t>Centre de post-cure</t>
+    <t>Centre de soins post-aigus (CeSPA)</t>
   </si>
   <si>
     <t>08</t>
@@ -312,7 +312,7 @@
     <t>36</t>
   </si>
   <si>
-    <t>Dispositif d'accueil familial</t>
+    <t>Dispositif d'accueil familial social PA-PH</t>
   </si>
   <si>
     <t>37</t>
@@ -942,7 +942,7 @@
     <t>145</t>
   </si>
   <si>
-    <t>Unité d'addictologie</t>
+    <t>Unité hospitalière d'addictologie</t>
   </si>
   <si>
     <t>146</t>
@@ -1014,7 +1014,7 @@
     <t>157</t>
   </si>
   <si>
-    <t>Unité hospitalière de gynécologie et/ou obstétrique</t>
+    <t>Unité hospitalière de gynécologie</t>
   </si>
   <si>
     <t>158</t>
@@ -1759,6 +1759,72 @@
   </si>
   <si>
     <t>Equipe mobile de psychiatrie périnatale</t>
+  </si>
+  <si>
+    <t>284</t>
+  </si>
+  <si>
+    <t>Equipe Spécialisée de Prévention et de Réadaptation à Domicile (ESPRAD)</t>
+  </si>
+  <si>
+    <t>285</t>
+  </si>
+  <si>
+    <t>Centre Anti-Poison et de Toxico-Vigilance (CAPTV)</t>
+  </si>
+  <si>
+    <t>286</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de Soins Intensifs Néonatals (USIN)</t>
+  </si>
+  <si>
+    <t>287</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de réanimation néonatale</t>
+  </si>
+  <si>
+    <t>288</t>
+  </si>
+  <si>
+    <t>Unité hospitalière « kangourou » ou « koala »</t>
+  </si>
+  <si>
+    <t>289</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de néonatalogie</t>
+  </si>
+  <si>
+    <t>290</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de maternité</t>
+  </si>
+  <si>
+    <t>291</t>
+  </si>
+  <si>
+    <t>Halte Soins Addiction (HSA)</t>
+  </si>
+  <si>
+    <t>292</t>
+  </si>
+  <si>
+    <t>Unité Hospitalière Sécurisée Interrégionale (UHSI)</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>Unité hospitalière dédiée grossesse pathologique (GHR)</t>
+  </si>
+  <si>
+    <t>294</t>
+  </si>
+  <si>
+    <t>Unité hospitalière de soins externes</t>
   </si>
   <si>
     <t/>
@@ -2029,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B280"/>
+  <dimension ref="A1:B291"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4265,15 +4331,103 @@
         <v>582</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="B281" t="s" s="2">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B283" t="s" s="2">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B285" t="s" s="2">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B286" t="s" s="2">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="B287" t="s" s="2">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B288" t="s" s="2">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B289" t="s" s="2">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="B290" t="s" s="2">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="B291" t="s" s="2">
+        <v>606</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -144,7 +144,7 @@
     <t>08</t>
   </si>
   <si>
-    <t>Centre de Ressources Autisme (CRA)</t>
+    <t>Centre de Référence Troubles du Neuro-développement (TND) - Centre de Diagnostic et d’évaluation expert (CDE)</t>
   </si>
   <si>
     <t>09</t>
@@ -1056,7 +1056,7 @@
     <t>164</t>
   </si>
   <si>
-    <t>Unité hospitalière de radiologie</t>
+    <t>Unité hospitalière d'imagerie médicale</t>
   </si>
   <si>
     <t>165</t>
@@ -1338,7 +1338,7 @@
     <t>211</t>
   </si>
   <si>
-    <t>Cabinet de ville de radiologie</t>
+    <t>Cabinet de ville d'imagerie médicale</t>
   </si>
   <si>
     <t>212</t>
@@ -1617,12 +1617,6 @@
     <t>Point d'information local dédié aux personnes âgées</t>
   </si>
   <si>
-    <t>260</t>
-  </si>
-  <si>
-    <t>Relayage au domicile</t>
-  </si>
-  <si>
     <t>261</t>
   </si>
   <si>
@@ -1825,6 +1819,12 @@
   </si>
   <si>
     <t>Unité hospitalière de soins externes</t>
+  </si>
+  <si>
+    <t>295</t>
+  </si>
+  <si>
+    <t>Permanence d'Accès aux Soins de Santé (PASS)</t>
   </si>
   <si>
     <t/>
